--- a/consent_forms/020_performing_arts_terms_acknowledgment--consent_forms.xlsx
+++ b/consent_forms/020_performing_arts_terms_acknowledgment--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_consent_organizations</t>
+          <t>participant_consent_organizations_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Participant Consent Organizations</t>
+          <t>Participant Consent Organizations 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>participant_consent_organizations</t>
+          <t>participant_consent_organizations_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Participant Consent Organizations</t>
+          <t>Participant Consent Organizations 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>participant_consent_organizations</t>
+          <t>participant_consent_organizations_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Participant Consent Organizations</t>
+          <t>Participant Consent Organizations 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>participant_consent_organizations</t>
+          <t>participant_consent_organizations_5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Participant Consent Organizations</t>
+          <t>Participant Consent Organizations 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -848,7 +848,7 @@
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1077,7 +1077,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>participant_consent_organizations_choices</t>
+          <t>participant_consent_organizations_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1094,7 +1094,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>participant_consent_organizations_choices</t>
+          <t>participant_consent_organizations_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1111,7 +1111,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>participant_consent_organizations_choices</t>
+          <t>participant_consent_organizations_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>participant_consent_organizations_choices</t>
+          <t>participant_consent_organizations_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>participant_consent_organizations_choices</t>
+          <t>participant_consent_organizations_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>participant_consent_organizations_choices</t>
+          <t>participant_consent_organizations_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>participant_consent_organizations_choices</t>
+          <t>participant_consent_organizations_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1196,7 +1196,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>participant_consent_organizations_choices</t>
+          <t>participant_consent_organizations_5_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
